--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_MEXICO_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/NEW_MEXICO_2015.xlsx
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C165">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C252">
@@ -12361,7 +12361,7 @@
         <v>82</v>
       </c>
       <c r="D667">
-        <v>0.009681227863046045</v>
+        <v>0.009681227863046043</v>
       </c>
     </row>
     <row r="668">
